--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/144.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/144.xlsx
@@ -426,13 +426,13 @@
         <v>-11.39574194744595</v>
       </c>
       <c r="E2">
-        <v>-11.5705112893238</v>
+        <v>-8.698670813983462</v>
       </c>
       <c r="F2">
-        <v>-5.318653170195139</v>
+        <v>-5.87542043916916</v>
       </c>
       <c r="G2">
-        <v>-13.49779268020511</v>
+        <v>-13.48511732132098</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.83530112980371</v>
       </c>
       <c r="E3">
-        <v>-12.07183147586894</v>
+        <v>-9.177783363994985</v>
       </c>
       <c r="F3">
-        <v>-5.27765064049137</v>
+        <v>-5.64904668043432</v>
       </c>
       <c r="G3">
-        <v>-14.10344547747976</v>
+        <v>-13.14465449109143</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.24789968073321</v>
       </c>
       <c r="E4">
-        <v>-12.31259685343475</v>
+        <v>-9.622062891939509</v>
       </c>
       <c r="F4">
-        <v>-5.369345941776858</v>
+        <v>-5.583801978687622</v>
       </c>
       <c r="G4">
-        <v>-13.45729584371844</v>
+        <v>-13.161162316757</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.54714867255756</v>
       </c>
       <c r="E5">
-        <v>-13.71404634695854</v>
+        <v>-10.39314880359558</v>
       </c>
       <c r="F5">
-        <v>-5.204551359031327</v>
+        <v>-5.327214347303072</v>
       </c>
       <c r="G5">
-        <v>-13.86298607732819</v>
+        <v>-13.55413453560234</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.69973999363443</v>
       </c>
       <c r="E6">
-        <v>-13.61695133576008</v>
+        <v>-10.23926219986692</v>
       </c>
       <c r="F6">
-        <v>-5.210909907215216</v>
+        <v>-5.331033121029978</v>
       </c>
       <c r="G6">
-        <v>-13.74537725297301</v>
+        <v>-13.59707916337235</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.68164820651282</v>
       </c>
       <c r="E7">
-        <v>-15.28186744705012</v>
+        <v>-12.20395876199074</v>
       </c>
       <c r="F7">
-        <v>-4.667508346285365</v>
+        <v>-5.132381505797226</v>
       </c>
       <c r="G7">
-        <v>-14.36683241327794</v>
+        <v>-12.91196010176029</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.48191393322737</v>
       </c>
       <c r="E8">
-        <v>-15.43687258385867</v>
+        <v>-12.89143092956918</v>
       </c>
       <c r="F8">
-        <v>-4.81269795770884</v>
+        <v>-4.836747120146916</v>
       </c>
       <c r="G8">
-        <v>-14.20644794406306</v>
+        <v>-12.98939036812007</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.10906991806822</v>
       </c>
       <c r="E9">
-        <v>-15.9877795607878</v>
+        <v>-12.76450233160819</v>
       </c>
       <c r="F9">
-        <v>-4.608213807592977</v>
+        <v>-4.742299153981925</v>
       </c>
       <c r="G9">
-        <v>-13.89706484444458</v>
+        <v>-12.97110083914772</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.587846534415</v>
       </c>
       <c r="E10">
-        <v>-16.44791327623318</v>
+        <v>-14.43070905799042</v>
       </c>
       <c r="F10">
-        <v>-4.621852876880071</v>
+        <v>-4.538104104089638</v>
       </c>
       <c r="G10">
-        <v>-13.68869743175516</v>
+        <v>-12.07396892769371</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.94867513891684</v>
       </c>
       <c r="E11">
-        <v>-16.99286983831623</v>
+        <v>-15.81505450518724</v>
       </c>
       <c r="F11">
-        <v>-4.465883720443966</v>
+        <v>-5.019594313701656</v>
       </c>
       <c r="G11">
-        <v>-13.2553465003993</v>
+        <v>-12.67478684500051</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.24101005641157</v>
       </c>
       <c r="E12">
-        <v>-16.77001457545076</v>
+        <v>-14.17653939736191</v>
       </c>
       <c r="F12">
-        <v>-4.457395439667479</v>
+        <v>-4.579430525447902</v>
       </c>
       <c r="G12">
-        <v>-13.26686686929451</v>
+        <v>-11.90475305065158</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.504191111128449</v>
       </c>
       <c r="E13">
-        <v>-18.17530874340705</v>
+        <v>-15.52192638267073</v>
       </c>
       <c r="F13">
-        <v>-4.33526674837054</v>
+        <v>-4.076429271119987</v>
       </c>
       <c r="G13">
-        <v>-12.66033306403116</v>
+        <v>-11.59315184525892</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.801500656635142</v>
       </c>
       <c r="E14">
-        <v>-19.43878469086513</v>
+        <v>-17.084834088464</v>
       </c>
       <c r="F14">
-        <v>-4.017191061410989</v>
+        <v>-4.366515251906346</v>
       </c>
       <c r="G14">
-        <v>-12.36946589767262</v>
+        <v>-11.11543223597624</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.170531338851008</v>
       </c>
       <c r="E15">
-        <v>-19.81906329565925</v>
+        <v>-18.36862477032049</v>
       </c>
       <c r="F15">
-        <v>-3.55660304647381</v>
+        <v>-4.186303923427313</v>
       </c>
       <c r="G15">
-        <v>-11.5166468833789</v>
+        <v>-11.4265806327937</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.662495699226792</v>
       </c>
       <c r="E16">
-        <v>-20.20616631078293</v>
+        <v>-16.87682769186967</v>
       </c>
       <c r="F16">
-        <v>-3.541700716897447</v>
+        <v>-4.298215531178124</v>
       </c>
       <c r="G16">
-        <v>-11.61962802202208</v>
+        <v>-9.541974936689478</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.290095458062139</v>
       </c>
       <c r="E17">
-        <v>-21.38401787170398</v>
+        <v>-18.88600292569683</v>
       </c>
       <c r="F17">
-        <v>-3.332674628312034</v>
+        <v>-3.210807701114379</v>
       </c>
       <c r="G17">
-        <v>-10.88691812291183</v>
+        <v>-9.600534897860888</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.072263681105216</v>
       </c>
       <c r="E18">
-        <v>-21.56544212587328</v>
+        <v>-19.5681767786863</v>
       </c>
       <c r="F18">
-        <v>-3.149342839826656</v>
+        <v>-2.986892536831048</v>
       </c>
       <c r="G18">
-        <v>-10.54825668331842</v>
+        <v>-9.535655303965989</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.988694925708653</v>
       </c>
       <c r="E19">
-        <v>-22.61065468310967</v>
+        <v>-21.17561749787099</v>
       </c>
       <c r="F19">
-        <v>-2.577680696582898</v>
+        <v>-3.479961665999397</v>
       </c>
       <c r="G19">
-        <v>-9.990350581566039</v>
+        <v>-8.58008483653826</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.024655497511559</v>
       </c>
       <c r="E20">
-        <v>-22.90420395370888</v>
+        <v>-20.73888693609726</v>
       </c>
       <c r="F20">
-        <v>-2.131102031161864</v>
+        <v>-2.771892262536644</v>
       </c>
       <c r="G20">
-        <v>-10.327883280943</v>
+        <v>-7.977170218654972</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.137827814906348</v>
       </c>
       <c r="E21">
-        <v>-24.01317742497327</v>
+        <v>-21.31913389612208</v>
       </c>
       <c r="F21">
-        <v>-2.298959088195545</v>
+        <v>-2.591961750607161</v>
       </c>
       <c r="G21">
-        <v>-10.18319453505772</v>
+        <v>-8.609589580800787</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.295026347380563</v>
       </c>
       <c r="E22">
-        <v>-24.61052390285106</v>
+        <v>-21.34947014349946</v>
       </c>
       <c r="F22">
-        <v>-1.655864338706177</v>
+        <v>-2.611999129713478</v>
       </c>
       <c r="G22">
-        <v>-10.17812504774838</v>
+        <v>-8.812273917749247</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.452566291206215</v>
       </c>
       <c r="E23">
-        <v>-25.04311996785579</v>
+        <v>-22.38305810795816</v>
       </c>
       <c r="F23">
-        <v>-1.624767426405083</v>
+        <v>-2.044786147790156</v>
       </c>
       <c r="G23">
-        <v>-9.585739869849352</v>
+        <v>-7.787797797573179</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.575483443234059</v>
       </c>
       <c r="E24">
-        <v>-25.09824055347715</v>
+        <v>-23.27722794314271</v>
       </c>
       <c r="F24">
-        <v>-1.526839488780931</v>
+        <v>-1.100340449203758</v>
       </c>
       <c r="G24">
-        <v>-10.0013164240177</v>
+        <v>-9.651256020726784</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.636325821305761</v>
       </c>
       <c r="E25">
-        <v>-25.6751953128984</v>
+        <v>-21.93915444335628</v>
       </c>
       <c r="F25">
-        <v>-1.125231232923078</v>
+        <v>-1.535181976894525</v>
       </c>
       <c r="G25">
-        <v>-9.907230677022186</v>
+        <v>-9.520607621894374</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.614474928061414</v>
       </c>
       <c r="E26">
-        <v>-26.16410295218852</v>
+        <v>-23.67920699538159</v>
       </c>
       <c r="F26">
-        <v>-1.167618792924328</v>
+        <v>-1.224561596560169</v>
       </c>
       <c r="G26">
-        <v>-9.478614548376601</v>
+        <v>-9.493796760532151</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.510006418685584</v>
       </c>
       <c r="E27">
-        <v>-25.49277479444742</v>
+        <v>-23.961063746093</v>
       </c>
       <c r="F27">
-        <v>-0.8705596153412034</v>
+        <v>-2.049742269961105</v>
       </c>
       <c r="G27">
-        <v>-10.20234374407864</v>
+        <v>-9.721789159368608</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.321839418100484</v>
       </c>
       <c r="E28">
-        <v>-26.04455123838602</v>
+        <v>-24.83260026818721</v>
       </c>
       <c r="F28">
-        <v>-1.005815444870307</v>
+        <v>-1.176102103496398</v>
       </c>
       <c r="G28">
-        <v>-10.51416807253735</v>
+        <v>-9.19616043409648</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.070544623463225</v>
       </c>
       <c r="E29">
-        <v>-26.14093075069127</v>
+        <v>-24.51788491007614</v>
       </c>
       <c r="F29">
-        <v>-1.085821653734891</v>
+        <v>-1.272145505279181</v>
       </c>
       <c r="G29">
-        <v>-10.23030631420823</v>
+        <v>-9.578973990993777</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.769363215969388</v>
       </c>
       <c r="E30">
-        <v>-25.8410325595333</v>
+        <v>-23.90565333813514</v>
       </c>
       <c r="F30">
-        <v>-0.9104960361975704</v>
+        <v>-0.6562518561955405</v>
       </c>
       <c r="G30">
-        <v>-10.00187423168281</v>
+        <v>-9.488888053079222</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.449350024112571</v>
       </c>
       <c r="E31">
-        <v>-26.10665020245321</v>
+        <v>-22.82790369515364</v>
       </c>
       <c r="F31">
-        <v>-1.039273204269379</v>
+        <v>-1.558170829057017</v>
       </c>
       <c r="G31">
-        <v>-10.61544297596961</v>
+        <v>-9.092706799548749</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.127606430512454</v>
       </c>
       <c r="E32">
-        <v>-25.73726257764753</v>
+        <v>-23.739671180332</v>
       </c>
       <c r="F32">
-        <v>-1.052121182686799</v>
+        <v>-0.8707211469847493</v>
       </c>
       <c r="G32">
-        <v>-10.45390515737659</v>
+        <v>-8.966704610444511</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.832512303553518</v>
       </c>
       <c r="E33">
-        <v>-25.03369168497182</v>
+        <v>-23.41196363029293</v>
       </c>
       <c r="F33">
-        <v>-1.199607028550834</v>
+        <v>-0.9296255246304194</v>
       </c>
       <c r="G33">
-        <v>-10.08646740470685</v>
+        <v>-9.817315362628722</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.574122209216566</v>
       </c>
       <c r="E34">
-        <v>-26.11961069506316</v>
+        <v>-23.0613737010931</v>
       </c>
       <c r="F34">
-        <v>-1.459002825430874</v>
+        <v>-1.334985456455552</v>
       </c>
       <c r="G34">
-        <v>-10.04294200072082</v>
+        <v>-8.634612176413112</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.369776847454792</v>
       </c>
       <c r="E35">
-        <v>-24.62094845001672</v>
+        <v>-22.83659383677436</v>
       </c>
       <c r="F35">
-        <v>-1.73824630528199</v>
+        <v>-1.399214579766417</v>
       </c>
       <c r="G35">
-        <v>-10.82471272458788</v>
+        <v>-9.534027818072504</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.219023630741304</v>
       </c>
       <c r="E36">
-        <v>-24.92869448662998</v>
+        <v>-21.466685164714</v>
       </c>
       <c r="F36">
-        <v>-1.412997784981598</v>
+        <v>-1.191535416577956</v>
       </c>
       <c r="G36">
-        <v>-9.88356322591391</v>
+        <v>-9.27688504690194</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.126865048958312</v>
       </c>
       <c r="E37">
-        <v>-23.87802058974034</v>
+        <v>-22.35494534131854</v>
       </c>
       <c r="F37">
-        <v>-1.187367071807069</v>
+        <v>-1.564767118685509</v>
       </c>
       <c r="G37">
-        <v>-10.2648969518879</v>
+        <v>-8.402770904687427</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.087094123378273</v>
       </c>
       <c r="E38">
-        <v>-24.02856970812534</v>
+        <v>-22.21803598664465</v>
       </c>
       <c r="F38">
-        <v>-1.5510642651084</v>
+        <v>-1.439841859036719</v>
       </c>
       <c r="G38">
-        <v>-9.923229913346038</v>
+        <v>-8.361939383601698</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.093574350461491</v>
       </c>
       <c r="E39">
-        <v>-23.8578688804062</v>
+        <v>-21.45211253535732</v>
       </c>
       <c r="F39">
-        <v>-1.235237595647449</v>
+        <v>-1.077007824569105</v>
       </c>
       <c r="G39">
-        <v>-10.00187423168281</v>
+        <v>-7.66783961858144</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.139083096267338</v>
       </c>
       <c r="E40">
-        <v>-24.22758255534043</v>
+        <v>-21.49986982224221</v>
       </c>
       <c r="F40">
-        <v>-1.397003667168345</v>
+        <v>-1.556668998955741</v>
       </c>
       <c r="G40">
-        <v>-9.865792129947959</v>
+        <v>-9.450245106773641</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.210273906081997</v>
       </c>
       <c r="E41">
-        <v>-21.79958687443987</v>
+        <v>-21.42741423811949</v>
       </c>
       <c r="F41">
-        <v>-1.314977898575735</v>
+        <v>-1.734645392182021</v>
       </c>
       <c r="G41">
-        <v>-9.383888963176991</v>
+        <v>-7.888278645388055</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.302296444942278</v>
       </c>
       <c r="E42">
-        <v>-22.99093328790378</v>
+        <v>-19.06101938914527</v>
       </c>
       <c r="F42">
-        <v>-1.134965378273375</v>
+        <v>-1.481942803916601</v>
       </c>
       <c r="G42">
-        <v>-9.429018884505593</v>
+        <v>-7.736764958659136</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.400082595348285</v>
       </c>
       <c r="E43">
-        <v>-21.3003724283083</v>
+        <v>-20.56140245431463</v>
       </c>
       <c r="F43">
-        <v>-1.520811459190759</v>
+        <v>-1.201924800543867</v>
       </c>
       <c r="G43">
-        <v>-9.609200603999382</v>
+        <v>-7.81520912248078</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.501783755193469</v>
       </c>
       <c r="E44">
-        <v>-21.04767452173228</v>
+        <v>-19.07775210060361</v>
       </c>
       <c r="F44">
-        <v>-1.65352171569106</v>
+        <v>-1.721493402927773</v>
       </c>
       <c r="G44">
-        <v>-8.975744375840781</v>
+        <v>-7.075940061473208</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.594179446504344</v>
       </c>
       <c r="E45">
-        <v>-21.61825318975073</v>
+        <v>-19.11581845311209</v>
       </c>
       <c r="F45">
-        <v>-1.952572288510515</v>
+        <v>-1.988045465800598</v>
       </c>
       <c r="G45">
-        <v>-9.379951497305658</v>
+        <v>-6.833805597715545</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.67923149431664</v>
       </c>
       <c r="E46">
-        <v>-20.91439700321254</v>
+        <v>-19.36976169004022</v>
       </c>
       <c r="F46">
-        <v>-1.648195313291059</v>
+        <v>-1.802321352255935</v>
       </c>
       <c r="G46">
-        <v>-8.855369481710992</v>
+        <v>-7.05311588430571</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.748686656990666</v>
       </c>
       <c r="E47">
-        <v>-20.21449870295704</v>
+        <v>-17.97502792346981</v>
       </c>
       <c r="F47">
-        <v>-1.770305780505137</v>
+        <v>-2.383937986579135</v>
       </c>
       <c r="G47">
-        <v>-8.460858369954277</v>
+        <v>-6.956359222960804</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.810922121945928</v>
       </c>
       <c r="E48">
-        <v>-19.7422830188592</v>
+        <v>-18.55071018169491</v>
       </c>
       <c r="F48">
-        <v>-1.861373179299303</v>
+        <v>-2.028295009535223</v>
       </c>
       <c r="G48">
-        <v>-8.94130139313129</v>
+        <v>-7.660817804444228</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.862916726267804</v>
       </c>
       <c r="E49">
-        <v>-18.89836113126376</v>
+        <v>-18.24734317944706</v>
       </c>
       <c r="F49">
-        <v>-2.062745981450252</v>
+        <v>-2.358422613838105</v>
       </c>
       <c r="G49">
-        <v>-9.057748665054424</v>
+        <v>-6.279978054361549</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.916396789960752</v>
       </c>
       <c r="E50">
-        <v>-19.07690074749017</v>
+        <v>-17.22876257784978</v>
       </c>
       <c r="F50">
-        <v>-2.245824289510373</v>
+        <v>-2.005026169190585</v>
       </c>
       <c r="G50">
-        <v>-8.942338259144075</v>
+        <v>-6.710753226793249</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.97082270867384</v>
       </c>
       <c r="E51">
-        <v>-18.59412466200644</v>
+        <v>-16.6146516891956</v>
       </c>
       <c r="F51">
-        <v>-2.165224141217982</v>
+        <v>-2.116297448939032</v>
       </c>
       <c r="G51">
-        <v>-8.883653611553406</v>
+        <v>-6.68054958233856</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.036775662042705</v>
       </c>
       <c r="E52">
-        <v>-18.53909917433924</v>
+        <v>-15.43138407336137</v>
       </c>
       <c r="F52">
-        <v>-2.107781832038253</v>
+        <v>-2.618954102427383</v>
       </c>
       <c r="G52">
-        <v>-8.369036665834775</v>
+        <v>-6.369660402024292</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.116186448854442</v>
       </c>
       <c r="E53">
-        <v>-18.44669113373872</v>
+        <v>-15.07883331491622</v>
       </c>
       <c r="F53">
-        <v>-2.439610902986484</v>
+        <v>-2.559984283756891</v>
       </c>
       <c r="G53">
-        <v>-8.663490207357786</v>
+        <v>-6.409448494654119</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.213581125820957</v>
       </c>
       <c r="E54">
-        <v>-17.97692535407903</v>
+        <v>-16.76546798754705</v>
       </c>
       <c r="F54">
-        <v>-1.993232702476929</v>
+        <v>-2.868151039844155</v>
       </c>
       <c r="G54">
-        <v>-8.434424849071391</v>
+        <v>-6.471758892067974</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.331656718052401</v>
       </c>
       <c r="E55">
-        <v>-17.85303989065119</v>
+        <v>-15.81189815880389</v>
       </c>
       <c r="F55">
-        <v>-2.389721647785481</v>
+        <v>-2.933703894264694</v>
       </c>
       <c r="G55">
-        <v>-8.700827227482707</v>
+        <v>-6.758097972674476</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.465614992496126</v>
       </c>
       <c r="E56">
-        <v>-17.5529515035849</v>
+        <v>-14.77060726005815</v>
       </c>
       <c r="F56">
-        <v>-2.391541570969431</v>
+        <v>-2.141171665310295</v>
       </c>
       <c r="G56">
-        <v>-8.722962348122721</v>
+        <v>-6.29119655087329</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.616927318764859</v>
       </c>
       <c r="E57">
-        <v>-16.77059422012374</v>
+        <v>-16.06235899922012</v>
       </c>
       <c r="F57">
-        <v>-2.226087607771273</v>
+        <v>-2.91325315982438</v>
       </c>
       <c r="G57">
-        <v>-8.590105687180804</v>
+        <v>-6.886561077948296</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.773829118573001</v>
       </c>
       <c r="E58">
-        <v>-16.37313911341852</v>
+        <v>-15.00999598152562</v>
       </c>
       <c r="F58">
-        <v>-2.223209031046544</v>
+        <v>-3.015378435078517</v>
       </c>
       <c r="G58">
-        <v>-8.674190270863134</v>
+        <v>-6.867582492448468</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.936535101437822</v>
       </c>
       <c r="E59">
-        <v>-16.61173082346065</v>
+        <v>-15.57827871322218</v>
       </c>
       <c r="F59">
-        <v>-2.523367131083542</v>
+        <v>-2.444691280267854</v>
       </c>
       <c r="G59">
-        <v>-8.875883678900642</v>
+        <v>-6.775399853957428</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.090983261387717</v>
       </c>
       <c r="E60">
-        <v>-16.18216883604106</v>
+        <v>-14.77164880907991</v>
       </c>
       <c r="F60">
-        <v>-2.207508983661285</v>
+        <v>-2.445817031568258</v>
       </c>
       <c r="G60">
-        <v>-8.898930979134182</v>
+        <v>-7.550706571352382</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.239651650722378</v>
       </c>
       <c r="E61">
-        <v>-16.09689767047663</v>
+        <v>-14.19632882877543</v>
       </c>
       <c r="F61">
-        <v>-2.498357890825622</v>
+        <v>-2.636542827491025</v>
       </c>
       <c r="G61">
-        <v>-9.285239036992285</v>
+        <v>-7.3940118357811</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.370574284278619</v>
       </c>
       <c r="E62">
-        <v>-15.56729716375358</v>
+        <v>-13.72274101705326</v>
       </c>
       <c r="F62">
-        <v>-2.321435180935704</v>
+        <v>-2.433178630103746</v>
       </c>
       <c r="G62">
-        <v>-9.323478393046054</v>
+        <v>-7.542641328759268</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.490094034529712</v>
       </c>
       <c r="E63">
-        <v>-15.25196140470347</v>
+        <v>-13.17501755735153</v>
       </c>
       <c r="F63">
-        <v>-2.346214135055646</v>
+        <v>-2.65969238292966</v>
       </c>
       <c r="G63">
-        <v>-9.590199049948637</v>
+        <v>-6.897077393046317</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.589617710640295</v>
       </c>
       <c r="E64">
-        <v>-14.79144276896744</v>
+        <v>-14.42816858407212</v>
       </c>
       <c r="F64">
-        <v>-2.344668401482022</v>
+        <v>-2.457398436226798</v>
       </c>
       <c r="G64">
-        <v>-9.370836263813521</v>
+        <v>-8.801271981860427</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.678644097832271</v>
       </c>
       <c r="E65">
-        <v>-14.77906644950447</v>
+        <v>-15.41323847801264</v>
       </c>
       <c r="F65">
-        <v>-2.473358590976536</v>
+        <v>-2.461181590155383</v>
       </c>
       <c r="G65">
-        <v>-9.825193575592948</v>
+        <v>-7.997953476012494</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.75462964624249</v>
       </c>
       <c r="E66">
-        <v>-15.4651710179326</v>
+        <v>-14.49470092419281</v>
       </c>
       <c r="F66">
-        <v>-2.796121180701127</v>
+        <v>-2.837831964534291</v>
       </c>
       <c r="G66">
-        <v>-9.987105453443748</v>
+        <v>-7.23050856547397</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.828714137741632</v>
       </c>
       <c r="E67">
-        <v>-14.49263141157131</v>
+        <v>-14.48503263218644</v>
       </c>
       <c r="F67">
-        <v>-2.416473773058891</v>
+        <v>-2.870810927574544</v>
       </c>
       <c r="G67">
-        <v>-9.56436599261113</v>
+        <v>-8.190318371156501</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.905885437710644</v>
       </c>
       <c r="E68">
-        <v>-14.34356763266082</v>
+        <v>-13.44102464903609</v>
       </c>
       <c r="F68">
-        <v>-2.427773532800479</v>
+        <v>-2.75405419888476</v>
       </c>
       <c r="G68">
-        <v>-9.718153565880744</v>
+        <v>-8.82247523557756</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.992431264966271</v>
       </c>
       <c r="E69">
-        <v>-14.53072493492383</v>
+        <v>-12.30150662058997</v>
       </c>
       <c r="F69">
-        <v>-2.544423402095303</v>
+        <v>-2.604789019839511</v>
       </c>
       <c r="G69">
-        <v>-9.770400456771782</v>
+        <v>-8.144227051910981</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.096559379441922</v>
       </c>
       <c r="E70">
-        <v>-14.94311042043233</v>
+        <v>-13.95329468573178</v>
       </c>
       <c r="F70">
-        <v>-2.557537286449022</v>
+        <v>-3.352994480702706</v>
       </c>
       <c r="G70">
-        <v>-10.13785461554932</v>
+        <v>-8.827721908851112</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.215665938597601</v>
       </c>
       <c r="E71">
-        <v>-15.41444305209868</v>
+        <v>-13.51659129480208</v>
       </c>
       <c r="F71">
-        <v>-2.618713875880571</v>
+        <v>-2.781763088508403</v>
       </c>
       <c r="G71">
-        <v>-9.792640576501698</v>
+        <v>-8.364682484825392</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.357615680953852</v>
       </c>
       <c r="E72">
-        <v>-15.43485741292526</v>
+        <v>-13.39449910708128</v>
       </c>
       <c r="F72">
-        <v>-2.59332275824996</v>
+        <v>-3.211946706293229</v>
       </c>
       <c r="G72">
-        <v>-9.798070998182579</v>
+        <v>-8.620732609216661</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.511683087243483</v>
       </c>
       <c r="E73">
-        <v>-15.49467855456658</v>
+        <v>-14.70757543034538</v>
       </c>
       <c r="F73">
-        <v>-2.586597243306631</v>
+        <v>-2.883463411284904</v>
       </c>
       <c r="G73">
-        <v>-9.569904694603471</v>
+        <v>-7.563811770260805</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.682346136279568</v>
       </c>
       <c r="E74">
-        <v>-15.39430945666058</v>
+        <v>-14.11805868402685</v>
       </c>
       <c r="F74">
-        <v>-2.492042417746679</v>
+        <v>-2.829347825594818</v>
       </c>
       <c r="G74">
-        <v>-9.03095092857844</v>
+        <v>-7.732643744380473</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.853818974993089</v>
       </c>
       <c r="E75">
-        <v>-15.74214154518974</v>
+        <v>-13.91506983663303</v>
       </c>
       <c r="F75">
-        <v>-2.970120582026566</v>
+        <v>-2.724590827101987</v>
       </c>
       <c r="G75">
-        <v>-9.4107818550782</v>
+        <v>-8.094637950483092</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.029100108634958</v>
       </c>
       <c r="E76">
-        <v>-16.05975059819171</v>
+        <v>-15.4940400397315</v>
       </c>
       <c r="F76">
-        <v>-2.727286334630696</v>
+        <v>-3.046486116155847</v>
       </c>
       <c r="G76">
-        <v>-9.521703549895228</v>
+        <v>-8.404221204616702</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.191037384156903</v>
       </c>
       <c r="E77">
-        <v>-15.86549717715868</v>
+        <v>-14.29100110637978</v>
       </c>
       <c r="F77">
-        <v>-2.73965303158709</v>
+        <v>-3.348053269145007</v>
       </c>
       <c r="G77">
-        <v>-8.795982652706604</v>
+        <v>-7.363752410559901</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.343174081008872</v>
       </c>
       <c r="E78">
-        <v>-16.77339734553448</v>
+        <v>-14.93236435161213</v>
       </c>
       <c r="F78">
-        <v>-2.889112876971997</v>
+        <v>-3.097580645927923</v>
       </c>
       <c r="G78">
-        <v>-9.391862331566442</v>
+        <v>-7.056160857912875</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.471044954816568</v>
       </c>
       <c r="E79">
-        <v>-17.11912369365008</v>
+        <v>-16.42674718872133</v>
       </c>
       <c r="F79">
-        <v>-2.819579717181006</v>
+        <v>-3.619240876003898</v>
       </c>
       <c r="G79">
-        <v>-9.22512705802326</v>
+        <v>-8.272660626190765</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.579492488440868</v>
       </c>
       <c r="E80">
-        <v>-17.61188053584671</v>
+        <v>-15.99867959772426</v>
       </c>
       <c r="F80">
-        <v>-3.067995504136939</v>
+        <v>-3.311884263236572</v>
       </c>
       <c r="G80">
-        <v>-8.540828301801064</v>
+        <v>-8.73867939939246</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.660714205375132</v>
       </c>
       <c r="E81">
-        <v>-18.10179802484054</v>
+        <v>-18.09314411101188</v>
       </c>
       <c r="F81">
-        <v>-3.176114845917733</v>
+        <v>-3.74883895617188</v>
       </c>
       <c r="G81">
-        <v>-7.794347115805831</v>
+        <v>-7.480599991513286</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.716946933280779</v>
       </c>
       <c r="E82">
-        <v>-18.86251373101904</v>
+        <v>-16.75123046526694</v>
       </c>
       <c r="F82">
-        <v>-3.423495173620166</v>
+        <v>-3.312557725935048</v>
       </c>
       <c r="G82">
-        <v>-8.211282095699792</v>
+        <v>-7.506646328252159</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.748118011186781</v>
       </c>
       <c r="E83">
-        <v>-19.61896814315633</v>
+        <v>-19.15265758916449</v>
       </c>
       <c r="F83">
-        <v>-3.479402518002507</v>
+        <v>-2.787560831960597</v>
       </c>
       <c r="G83">
-        <v>-8.888657474431559</v>
+        <v>-7.821541880090509</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.753024437868545</v>
       </c>
       <c r="E84">
-        <v>-20.35979931996715</v>
+        <v>-20.27090537519658</v>
       </c>
       <c r="F84">
-        <v>-3.665924349356067</v>
+        <v>-3.714403723237505</v>
       </c>
       <c r="G84">
-        <v>-8.724714520435464</v>
+        <v>-6.691174177748042</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.741050726689103</v>
       </c>
       <c r="E85">
-        <v>-22.47054369731234</v>
+        <v>-20.27527082413998</v>
       </c>
       <c r="F85">
-        <v>-3.843187518248536</v>
+        <v>-3.498348937239338</v>
       </c>
       <c r="G85">
-        <v>-7.944610657120601</v>
+        <v>-6.339128635413659</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.709906869364787</v>
       </c>
       <c r="E86">
-        <v>-22.62477899353959</v>
+        <v>-21.845120680587</v>
       </c>
       <c r="F86">
-        <v>-3.289297997631841</v>
+        <v>-4.125655004031348</v>
       </c>
       <c r="G86">
-        <v>-8.04153137954348</v>
+        <v>-7.448194647392211</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.675979795589601</v>
       </c>
       <c r="E87">
-        <v>-23.60377620383582</v>
+        <v>-22.72935957227273</v>
       </c>
       <c r="F87">
-        <v>-3.880272698504467</v>
+        <v>-3.911809473896447</v>
       </c>
       <c r="G87">
-        <v>-8.352873368432951</v>
+        <v>-6.851350289393896</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.636616835044894</v>
       </c>
       <c r="E88">
-        <v>-24.83862313861741</v>
+        <v>-23.6389488614534</v>
       </c>
       <c r="F88">
-        <v>-3.667651495390904</v>
+        <v>-3.76581468935745</v>
       </c>
       <c r="G88">
-        <v>-7.788890444352474</v>
+        <v>-6.552719752825713</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.610343312794136</v>
       </c>
       <c r="E89">
-        <v>-26.59761829741681</v>
+        <v>-25.72979059553488</v>
       </c>
       <c r="F89">
-        <v>-3.588830680279725</v>
+        <v>-4.150105924659781</v>
       </c>
       <c r="G89">
-        <v>-7.900570101349735</v>
+        <v>-7.024316602678464</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.592703311603053</v>
       </c>
       <c r="E90">
-        <v>-27.65373089158966</v>
+        <v>-26.83354273626842</v>
       </c>
       <c r="F90">
-        <v>-3.742543363910604</v>
+        <v>-4.024756540900756</v>
       </c>
       <c r="G90">
-        <v>-7.943465510796355</v>
+        <v>-7.279110019212465</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.600871053104941</v>
       </c>
       <c r="E91">
-        <v>-29.71288236456546</v>
+        <v>-28.23423144615892</v>
       </c>
       <c r="F91">
-        <v>-4.164227103775303</v>
+        <v>-3.993583418798606</v>
       </c>
       <c r="G91">
-        <v>-8.415262515164233</v>
+        <v>-7.277439877438708</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.627949115261469</v>
       </c>
       <c r="E92">
-        <v>-31.33588744891452</v>
+        <v>-30.75761037508303</v>
       </c>
       <c r="F92">
-        <v>-3.897531733341794</v>
+        <v>-3.831768473600945</v>
       </c>
       <c r="G92">
-        <v>-8.724366710950163</v>
+        <v>-7.008862049133479</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.688102025644687</v>
       </c>
       <c r="E93">
-        <v>-33.25359430049775</v>
+        <v>-32.68945738675521</v>
       </c>
       <c r="F93">
-        <v>-4.244507502250215</v>
+        <v>-4.291579479914297</v>
       </c>
       <c r="G93">
-        <v>-8.341966587969356</v>
+        <v>-6.860403179676403</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.772246882321411</v>
       </c>
       <c r="E94">
-        <v>-34.61185120893636</v>
+        <v>-35.30332201906359</v>
       </c>
       <c r="F94">
-        <v>-4.073216033964528</v>
+        <v>-4.453803638608941</v>
       </c>
       <c r="G94">
-        <v>-8.613103769090952</v>
+        <v>-8.268385194498808</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.88805372326491</v>
       </c>
       <c r="E95">
-        <v>-37.58016176606211</v>
+        <v>-37.498624327317</v>
       </c>
       <c r="F95">
-        <v>-4.009442512725202</v>
+        <v>-4.152692916058723</v>
       </c>
       <c r="G95">
-        <v>-8.710844796903691</v>
+        <v>-8.545467949086119</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.02783008778366</v>
       </c>
       <c r="E96">
-        <v>-38.63144247846878</v>
+        <v>-40.30322602059145</v>
       </c>
       <c r="F96">
-        <v>-4.075890832308168</v>
+        <v>-4.474152483858711</v>
       </c>
       <c r="G96">
-        <v>-8.707757167416254</v>
+        <v>-8.729803695074162</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.18662867621599</v>
       </c>
       <c r="E97">
-        <v>-40.68748741827532</v>
+        <v>-41.42729968843442</v>
       </c>
       <c r="F97">
-        <v>-3.909935706831314</v>
+        <v>-4.346704845468396</v>
       </c>
       <c r="G97">
-        <v>-9.571715928904284</v>
+        <v>-8.242814634886056</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.35917371137537</v>
       </c>
       <c r="E98">
-        <v>-43.59065587680072</v>
+        <v>-43.35826364767509</v>
       </c>
       <c r="F98">
-        <v>-3.905204900593926</v>
+        <v>-3.954814995980186</v>
       </c>
       <c r="G98">
-        <v>-9.799045520985734</v>
+        <v>-8.491839663918554</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.52749202578799</v>
       </c>
       <c r="E99">
-        <v>-45.49969975760727</v>
+        <v>-46.21998524784529</v>
       </c>
       <c r="F99">
-        <v>-3.861944241350125</v>
+        <v>-4.504401147939338</v>
       </c>
       <c r="G99">
-        <v>-9.62233205268028</v>
+        <v>-8.807512865266492</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.69025324343962</v>
       </c>
       <c r="E100">
-        <v>-47.98949552329051</v>
+        <v>-47.86628706672681</v>
       </c>
       <c r="F100">
-        <v>-3.80542639019192</v>
+        <v>-4.123229544275951</v>
       </c>
       <c r="G100">
-        <v>-10.65801682570341</v>
+        <v>-10.7544913019942</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.82044067189601</v>
       </c>
       <c r="E101">
-        <v>-50.61106422200444</v>
+        <v>-50.38452617765222</v>
       </c>
       <c r="F101">
-        <v>-3.826114037709435</v>
+        <v>-4.235977803103588</v>
       </c>
       <c r="G101">
-        <v>-11.09157447401752</v>
+        <v>-10.96810210673561</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.92477146583862</v>
       </c>
       <c r="E102">
-        <v>-51.96619195490376</v>
+        <v>-53.28797087309209</v>
       </c>
       <c r="F102">
-        <v>-3.782116959844545</v>
+        <v>-4.050197360575535</v>
       </c>
       <c r="G102">
-        <v>-11.05807648311715</v>
+        <v>-10.9378361190713</v>
       </c>
     </row>
   </sheetData>
